--- a/data/trans_dic/P32E$bar_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32E$bar_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,76; 60,76</t>
+          <t>25,73; 61,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,59; 100,0</t>
+          <t>20,75; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,77; 64,86</t>
+          <t>32,37; 64,8</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,83; 82,22</t>
+          <t>62,48; 84,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,6; 82,29</t>
+          <t>50,4; 82,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,32; 80,66</t>
+          <t>62,4; 81,01</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,11; 83,39</t>
+          <t>46,81; 84,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54,54; 94,3</t>
+          <t>54,65; 93,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,88; 84,1</t>
+          <t>57,87; 84,85</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,76; 74,47</t>
+          <t>57,42; 74,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,65; 84,03</t>
+          <t>60,95; 84,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,63; 75,59</t>
+          <t>61,61; 75,43</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6978; 16459</t>
+          <t>6970; 16552</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1223; 4976</t>
+          <t>1032; 4976</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10188; 20796</t>
+          <t>10378; 20779</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56633; 75307</t>
+          <t>57223; 76952</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11153; 18884</t>
+          <t>11566; 18956</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72528; 92383</t>
+          <t>71468; 92784</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11651; 21071</t>
+          <t>11828; 21238</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14264; 24662</t>
+          <t>14292; 24418</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29249; 43249</t>
+          <t>29760; 43635</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83144; 107201</t>
+          <t>82656; 106927</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32260; 45441</t>
+          <t>32959; 45558</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>122047; 149697</t>
+          <t>122013; 149368</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$bar_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32E$bar_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,73; 61,1</t>
+          <t>27,23; 62,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,75; 100,0</t>
+          <t>12,26; 92,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,37; 64,8</t>
+          <t>31,13; 63,45</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,48; 84,02</t>
+          <t>61,73; 81,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,4; 82,6</t>
+          <t>49,65; 81,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,4; 81,01</t>
+          <t>62,15; 79,33</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>72,54%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,81; 84,05</t>
+          <t>42,85; 81,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54,65; 93,36</t>
+          <t>52,95; 91,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,87; 84,85</t>
+          <t>56,3; 83,27</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,42; 74,28</t>
+          <t>57,37; 74,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,95; 84,24</t>
+          <t>60,01; 81,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,61; 75,43</t>
+          <t>60,24; 74,09</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>16347</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6970; 16552</t>
+          <t>7941; 18110</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1032; 4976</t>
+          <t>714; 5367</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10378; 20779</t>
+          <t>10894; 22204</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>67277</t>
+          <t>75673</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83097</t>
+          <t>95796</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57223; 76952</t>
+          <t>64538; 85432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11566; 18956</t>
+          <t>14924; 24642</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71468; 92784</t>
+          <t>83654; 106771</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37648</t>
+          <t>39533</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11828; 21238</t>
+          <t>11534; 21999</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14292; 24418</t>
+          <t>14602; 25195</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29760; 43635</t>
+          <t>30679; 45377</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>95952</t>
+          <t>106085</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>40062</t>
+          <t>45591</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136014</t>
+          <t>151676</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82656; 106927</t>
+          <t>92142; 118944</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32959; 45558</t>
+          <t>38081; 51984</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>122013; 149368</t>
+          <t>134982; 166030</t>
         </is>
       </c>
     </row>
